--- a/outputs/37086.xlsx
+++ b/outputs/37086.xlsx
@@ -113,8 +113,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -136,7 +144,6 @@
         <color rgb="FF000000"/>
         <sz val="11"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
 </styleSheet>
@@ -323,75 +330,75 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <f aca="false">SUM(B2:C2)+IF(A2="A",10,-10)</f>
         <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">SUM(B3:C3)+IF(A3="A",10,-10)</f>
         <v>410</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">SUM(B4:C4)+IF(A4="A",10,-10)</f>
         <v>590</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">SUM(B5:C5)+IF(A5="A",10,-10)</f>
         <v>790</v>
       </c>

--- a/outputs/37086.xlsx
+++ b/outputs/37086.xlsx
@@ -354,7 +354,7 @@
         <v>100</v>
       </c>
       <c r="D2" s="2" t="n">
-        <f aca="false">SUM(B2:C2)+IF(A2="A",10,-10)</f>
+        <f aca="false">IF(A2="A",B2+C2+10,B2+C2-10)</f>
         <v>210</v>
       </c>
     </row>
@@ -369,7 +369,7 @@
         <v>200</v>
       </c>
       <c r="D3" s="1" t="n">
-        <f aca="false">SUM(B3:C3)+IF(A3="A",10,-10)</f>
+        <f aca="false">IF(A3="A",B3+C3+10,B3+C3-10)</f>
         <v>410</v>
       </c>
     </row>
@@ -384,7 +384,7 @@
         <v>300</v>
       </c>
       <c r="D4" s="1" t="n">
-        <f aca="false">SUM(B4:C4)+IF(A4="A",10,-10)</f>
+        <f aca="false">IF(A4="A",B4+C4+10,B4+C4-10)</f>
         <v>590</v>
       </c>
     </row>
@@ -399,7 +399,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="1" t="n">
-        <f aca="false">SUM(B5:C5)+IF(A5="A",10,-10)</f>
+        <f aca="false">IF(A5="A",B5+C5+10,B5+C5-10)</f>
         <v>790</v>
       </c>
     </row>
